--- a/data/BaseScene.xlsx
+++ b/data/BaseScene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,11 +427,39 @@
           <t>nav_bin_file</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spawn_x</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>spawn_y</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>spawn_z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>服务器出生 X（Unity Z）</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>服务器出生 Y（Unity X）</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>服务器出生 Z（Unity Y）</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>
@@ -441,6 +469,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -448,8 +485,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>data/scene_nav_bin/main_scene.bin</t>
-        </is>
+          <t>data/scene_nav_bin/penglai_scene.bin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>170</v>
+      </c>
+      <c r="D7" t="n">
+        <v>220</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -458,8 +504,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>data/scene_nav_bin/main_scene.bin</t>
-        </is>
+          <t>data/scene_nav_bin/donghai_scene.bin</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>180</v>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -468,8 +523,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>data/scene_nav_bin/main_scene.bin</t>
-        </is>
+          <t>data/scene_nav_bin/lanxian_scene.bin</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>180</v>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -481,6 +545,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>180</v>
+      </c>
+      <c r="D10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -491,6 +564,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>180</v>
+      </c>
+      <c r="D11" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -501,6 +583,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>180</v>
+      </c>
+      <c r="D12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -511,6 +602,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>180</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -521,6 +621,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>180</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -531,6 +640,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>180</v>
+      </c>
+      <c r="D15" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -541,6 +659,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>180</v>
+      </c>
+      <c r="D16" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -551,6 +678,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>180</v>
+      </c>
+      <c r="D17" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -561,6 +697,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>180</v>
+      </c>
+      <c r="D18" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -571,6 +716,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>180</v>
+      </c>
+      <c r="D19" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -581,6 +735,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>180</v>
+      </c>
+      <c r="D20" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -591,6 +754,15 @@
           <t>data/scene_nav_bin/main_scene.bin</t>
         </is>
       </c>
+      <c r="C21" t="n">
+        <v>180</v>
+      </c>
+      <c r="D21" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -601,6 +773,15 @@
           <t>data/scene_nav_bin/dungeon_scene.bin</t>
         </is>
       </c>
+      <c r="C22" t="n">
+        <v>180</v>
+      </c>
+      <c r="D22" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -611,6 +792,15 @@
           <t>data/scene_nav_bin/dungeon_scene.bin</t>
         </is>
       </c>
+      <c r="C23" t="n">
+        <v>180</v>
+      </c>
+      <c r="D23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -621,6 +811,15 @@
           <t>data/scene_nav_bin/dungeon_scene.bin</t>
         </is>
       </c>
+      <c r="C24" t="n">
+        <v>180</v>
+      </c>
+      <c r="D24" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -631,6 +830,15 @@
           <t>data/scene_nav_bin/mirror_scene.bin</t>
         </is>
       </c>
+      <c r="C25" t="n">
+        <v>180</v>
+      </c>
+      <c r="D25" t="n">
+        <v>200</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -640,6 +848,15 @@
         <is>
           <t>data/scene_nav_bin/mirror_scene.bin</t>
         </is>
+      </c>
+      <c r="C26" t="n">
+        <v>180</v>
+      </c>
+      <c r="D26" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
